--- a/analyst/Franzi/rmonize/data_dictionary/DD_CARLA_FRANZI.xlsx
+++ b/analyst/Franzi/rmonize/data_dictionary/DD_CARLA_FRANZI.xlsx
@@ -1,27 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Projekte\NFDI4Health\TA5\Pilotprojekte\Harmonisierung\HarmonizR\use-cases-harmonisation\analyst\Franzi\rmonize\data_dictionary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Franzi\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{D8381B53-48B1-4985-A7B6-AE3B4B802171}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745B7B05-FDF9-4E41-9436-4583A9EF577A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="1" r:id="rId1"/>
     <sheet name="Categories" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="196">
   <si>
     <t>index</t>
   </si>
@@ -248,12 +253,6 @@
     <t>Intake of breakfast cereals [g/d]</t>
   </si>
   <si>
-    <t>SALT_BISCUIT_0605</t>
-  </si>
-  <si>
-    <t>Intake of crackers and breadsticks [g/d]</t>
-  </si>
-  <si>
     <t>DOUGH_PASTRY_0606</t>
   </si>
   <si>
@@ -290,12 +289,6 @@
     <t>Intake of pig fresh meat [g/d]</t>
   </si>
   <si>
-    <t>MUTTON_LAMB_070104</t>
-  </si>
-  <si>
-    <t>Intake of lamb and sheep meat [g/d]</t>
-  </si>
-  <si>
     <t>POULTRY_0702</t>
   </si>
   <si>
@@ -314,12 +307,6 @@
     <t>Intake of chicken meat [g/d]</t>
   </si>
   <si>
-    <t>RABBIT_070205</t>
-  </si>
-  <si>
-    <t>Intake of rabbit meat [g/d]</t>
-  </si>
-  <si>
     <t>PROCMEAT_0704</t>
   </si>
   <si>
@@ -494,12 +481,6 @@
     <t>Intake of herbal and other non-tea infusions [g/d]</t>
   </si>
   <si>
-    <t>COFFEE_IMITATE_130304</t>
-  </si>
-  <si>
-    <t>Intake of chicory coffee infusion and coffee imitate beverages [g/d]</t>
-  </si>
-  <si>
     <t>WATER_1304</t>
   </si>
   <si>
@@ -582,12 +563,6 @@
   </si>
   <si>
     <t>Intakes of berbs, spices and similar [g/d]</t>
-  </si>
-  <si>
-    <t>CONDIMENTS_1504</t>
-  </si>
-  <si>
-    <t>Condiments intake [g/d]</t>
   </si>
   <si>
     <t>SOUP_BOUILLON_16</t>
@@ -705,9 +680,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -745,9 +720,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -780,26 +755,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -832,26 +790,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1025,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.140625" bestFit="1" customWidth="1"/>
@@ -1057,7 +998,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1071,7 +1012,7 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1085,7 +1026,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1099,7 +1040,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1113,7 +1054,7 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1127,7 +1068,7 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1141,7 +1082,7 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1155,7 +1096,7 @@
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1169,7 +1110,7 @@
         <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1183,7 +1124,7 @@
         <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1197,7 +1138,7 @@
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1211,7 +1152,7 @@
         <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1225,7 +1166,7 @@
         <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1239,7 +1180,7 @@
         <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1253,7 +1194,7 @@
         <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1267,7 +1208,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1281,7 +1222,7 @@
         <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1295,7 +1236,7 @@
         <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1309,7 +1250,7 @@
         <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1323,7 +1264,7 @@
         <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1337,7 +1278,7 @@
         <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1351,7 +1292,7 @@
         <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1365,7 +1306,7 @@
         <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1379,7 +1320,7 @@
         <v>52</v>
       </c>
       <c r="D25" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1393,7 +1334,7 @@
         <v>54</v>
       </c>
       <c r="D26" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1407,7 +1348,7 @@
         <v>56</v>
       </c>
       <c r="D27" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1421,7 +1362,7 @@
         <v>58</v>
       </c>
       <c r="D28" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1435,7 +1376,7 @@
         <v>60</v>
       </c>
       <c r="D29" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1449,7 +1390,7 @@
         <v>62</v>
       </c>
       <c r="D30" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1463,7 +1404,7 @@
         <v>64</v>
       </c>
       <c r="D31" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1477,7 +1418,7 @@
         <v>66</v>
       </c>
       <c r="D32" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1491,7 +1432,7 @@
         <v>68</v>
       </c>
       <c r="D33" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1505,7 +1446,7 @@
         <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1519,7 +1460,7 @@
         <v>72</v>
       </c>
       <c r="D35" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1533,7 +1474,7 @@
         <v>74</v>
       </c>
       <c r="D36" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1547,7 +1488,7 @@
         <v>76</v>
       </c>
       <c r="D37" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1561,7 +1502,7 @@
         <v>78</v>
       </c>
       <c r="D38" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1575,7 +1516,7 @@
         <v>80</v>
       </c>
       <c r="D39" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1589,7 +1530,7 @@
         <v>82</v>
       </c>
       <c r="D40" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1603,7 +1544,7 @@
         <v>84</v>
       </c>
       <c r="D41" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1617,7 +1558,7 @@
         <v>86</v>
       </c>
       <c r="D42" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1631,7 +1572,7 @@
         <v>88</v>
       </c>
       <c r="D43" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1645,7 +1586,7 @@
         <v>90</v>
       </c>
       <c r="D44" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1659,7 +1600,7 @@
         <v>92</v>
       </c>
       <c r="D45" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1673,7 +1614,7 @@
         <v>94</v>
       </c>
       <c r="D46" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1687,7 +1628,7 @@
         <v>96</v>
       </c>
       <c r="D47" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1701,7 +1642,7 @@
         <v>98</v>
       </c>
       <c r="D48" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1715,7 +1656,7 @@
         <v>100</v>
       </c>
       <c r="D49" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1729,7 +1670,7 @@
         <v>102</v>
       </c>
       <c r="D50" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1743,7 +1684,7 @@
         <v>104</v>
       </c>
       <c r="D51" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1757,7 +1698,7 @@
         <v>106</v>
       </c>
       <c r="D52" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1771,7 +1712,7 @@
         <v>108</v>
       </c>
       <c r="D53" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1785,7 +1726,7 @@
         <v>110</v>
       </c>
       <c r="D54" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1799,7 +1740,7 @@
         <v>112</v>
       </c>
       <c r="D55" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1813,7 +1754,7 @@
         <v>114</v>
       </c>
       <c r="D56" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1827,7 +1768,7 @@
         <v>116</v>
       </c>
       <c r="D57" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -1841,7 +1782,7 @@
         <v>118</v>
       </c>
       <c r="D58" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -1855,7 +1796,7 @@
         <v>120</v>
       </c>
       <c r="D59" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -1869,7 +1810,7 @@
         <v>122</v>
       </c>
       <c r="D60" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -1883,7 +1824,7 @@
         <v>124</v>
       </c>
       <c r="D61" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -1897,7 +1838,7 @@
         <v>126</v>
       </c>
       <c r="D62" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1911,7 +1852,7 @@
         <v>128</v>
       </c>
       <c r="D63" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -1925,7 +1866,7 @@
         <v>130</v>
       </c>
       <c r="D64" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1939,7 +1880,7 @@
         <v>132</v>
       </c>
       <c r="D65" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1953,7 +1894,7 @@
         <v>134</v>
       </c>
       <c r="D66" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -1967,7 +1908,7 @@
         <v>136</v>
       </c>
       <c r="D67" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -1981,7 +1922,7 @@
         <v>138</v>
       </c>
       <c r="D68" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1995,7 +1936,7 @@
         <v>140</v>
       </c>
       <c r="D69" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -2009,7 +1950,7 @@
         <v>142</v>
       </c>
       <c r="D70" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -2023,7 +1964,7 @@
         <v>144</v>
       </c>
       <c r="D71" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -2037,7 +1978,7 @@
         <v>146</v>
       </c>
       <c r="D72" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -2051,7 +1992,7 @@
         <v>148</v>
       </c>
       <c r="D73" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -2065,7 +2006,7 @@
         <v>150</v>
       </c>
       <c r="D74" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -2079,7 +2020,7 @@
         <v>152</v>
       </c>
       <c r="D75" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -2093,7 +2034,7 @@
         <v>154</v>
       </c>
       <c r="D76" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -2107,7 +2048,7 @@
         <v>156</v>
       </c>
       <c r="D77" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -2121,7 +2062,7 @@
         <v>158</v>
       </c>
       <c r="D78" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -2135,7 +2076,7 @@
         <v>160</v>
       </c>
       <c r="D79" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -2149,7 +2090,7 @@
         <v>162</v>
       </c>
       <c r="D80" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -2163,7 +2104,7 @@
         <v>164</v>
       </c>
       <c r="D81" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -2177,7 +2118,7 @@
         <v>166</v>
       </c>
       <c r="D82" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -2191,7 +2132,7 @@
         <v>168</v>
       </c>
       <c r="D83" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -2205,7 +2146,7 @@
         <v>170</v>
       </c>
       <c r="D84" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -2219,7 +2160,7 @@
         <v>172</v>
       </c>
       <c r="D85" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -2233,7 +2174,7 @@
         <v>174</v>
       </c>
       <c r="D86" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -2247,7 +2188,7 @@
         <v>176</v>
       </c>
       <c r="D87" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -2261,7 +2202,7 @@
         <v>178</v>
       </c>
       <c r="D88" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -2275,7 +2216,7 @@
         <v>180</v>
       </c>
       <c r="D89" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -2289,7 +2230,7 @@
         <v>182</v>
       </c>
       <c r="D90" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -2303,7 +2244,7 @@
         <v>184</v>
       </c>
       <c r="D91" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -2317,7 +2258,7 @@
         <v>186</v>
       </c>
       <c r="D92" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -2331,7 +2272,7 @@
         <v>188</v>
       </c>
       <c r="D93" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -2345,7 +2286,7 @@
         <v>190</v>
       </c>
       <c r="D94" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -2359,7 +2300,7 @@
         <v>192</v>
       </c>
       <c r="D95" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -2373,77 +2314,7 @@
         <v>194</v>
       </c>
       <c r="D96" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>96</v>
-      </c>
-      <c r="B97" t="s">
-        <v>195</v>
-      </c>
-      <c r="C97" t="s">
-        <v>196</v>
-      </c>
-      <c r="D97" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>97</v>
-      </c>
-      <c r="B98" t="s">
-        <v>197</v>
-      </c>
-      <c r="C98" t="s">
-        <v>198</v>
-      </c>
-      <c r="D98" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>98</v>
-      </c>
-      <c r="B99" t="s">
-        <v>199</v>
-      </c>
-      <c r="C99" t="s">
-        <v>200</v>
-      </c>
-      <c r="D99" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>99</v>
-      </c>
-      <c r="B100" t="s">
-        <v>201</v>
-      </c>
-      <c r="C100" t="s">
-        <v>202</v>
-      </c>
-      <c r="D100" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>100</v>
-      </c>
-      <c r="B101" t="s">
-        <v>203</v>
-      </c>
-      <c r="C101" t="s">
-        <v>204</v>
-      </c>
-      <c r="D101" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
